--- a/public/data/builtin/practice/Flow Data/시도간_인구이동_예시.xlsx
+++ b/public/data/builtin/practice/Flow Data/시도간_인구이동_예시.xlsx
@@ -460,40 +460,40 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="D2">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="E2">
-        <v>3572</v>
+        <v>10084</v>
       </c>
       <c r="F2">
-        <v>757</v>
+        <v>770</v>
       </c>
       <c r="G2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I2">
         <v>73682</v>
       </c>
       <c r="J2">
-        <v>1030</v>
+        <v>1008</v>
       </c>
       <c r="K2">
-        <v>901</v>
+        <v>1050</v>
       </c>
       <c r="L2">
-        <v>1407</v>
+        <v>1438</v>
       </c>
       <c r="M2">
-        <v>709</v>
+        <v>853</v>
       </c>
       <c r="N2">
-        <v>731</v>
+        <v>789</v>
       </c>
       <c r="O2">
         <v>84</v>
@@ -502,7 +502,7 @@
         <v>587</v>
       </c>
       <c r="Q2">
-        <v>636</v>
+        <v>705</v>
       </c>
     </row>
     <row r="3">
@@ -510,52 +510,52 @@
         <v>부산광역시</v>
       </c>
       <c r="B3">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>804</v>
+        <v>789</v>
       </c>
       <c r="E3">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="F3">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G3">
-        <v>1053</v>
+        <v>958</v>
       </c>
       <c r="H3">
         <v>46</v>
       </c>
       <c r="I3">
-        <v>1072</v>
+        <v>1091</v>
       </c>
       <c r="J3">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K3">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="L3">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M3">
-        <v>472</v>
+        <v>571</v>
       </c>
       <c r="N3">
-        <v>1871</v>
+        <v>1413</v>
       </c>
       <c r="O3">
         <v>54</v>
       </c>
       <c r="P3">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="Q3">
-        <v>342</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4">
@@ -563,52 +563,52 @@
         <v>대구광역시</v>
       </c>
       <c r="B4">
-        <v>800</v>
+        <v>816</v>
       </c>
       <c r="C4">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="F4">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G4">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="H4">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I4">
-        <v>1222</v>
+        <v>1266</v>
       </c>
       <c r="J4">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="K4">
-        <v>382</v>
+        <v>332</v>
       </c>
       <c r="L4">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M4">
-        <v>647</v>
+        <v>1579</v>
       </c>
       <c r="N4">
-        <v>979</v>
+        <v>1084</v>
       </c>
       <c r="O4">
         <v>35</v>
       </c>
       <c r="P4">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="Q4">
-        <v>261</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5">
@@ -616,52 +616,52 @@
         <v>인천광역시</v>
       </c>
       <c r="B5">
-        <v>4005</v>
+        <v>11304</v>
       </c>
       <c r="C5">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="D5">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="G5">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="H5">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="I5">
-        <v>4531</v>
+        <v>10217</v>
       </c>
       <c r="J5">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="K5">
-        <v>201</v>
+        <v>325</v>
       </c>
       <c r="L5">
-        <v>369</v>
+        <v>550</v>
       </c>
       <c r="M5">
-        <v>186</v>
+        <v>276</v>
       </c>
       <c r="N5">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="O5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P5">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="Q5">
-        <v>212</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
@@ -669,16 +669,16 @@
         <v>대전광역시</v>
       </c>
       <c r="B6">
-        <v>913</v>
+        <v>928</v>
       </c>
       <c r="C6">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D6">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E6">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -690,31 +690,31 @@
         <v>244</v>
       </c>
       <c r="I6">
-        <v>1338</v>
+        <v>1412</v>
       </c>
       <c r="J6">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K6">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L6">
-        <v>701</v>
+        <v>680</v>
       </c>
       <c r="M6">
-        <v>190</v>
+        <v>299</v>
       </c>
       <c r="N6">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="O6">
         <v>23</v>
       </c>
       <c r="P6">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="Q6">
-        <v>210</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
@@ -722,19 +722,19 @@
         <v>울산광역시</v>
       </c>
       <c r="B7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C7">
-        <v>1175</v>
+        <v>1069</v>
       </c>
       <c r="D7">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="E7">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F7">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -743,31 +743,31 @@
         <v>18</v>
       </c>
       <c r="I7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="J7">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K7">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="L7">
         <v>86</v>
       </c>
       <c r="M7">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="N7">
-        <v>492</v>
+        <v>418</v>
       </c>
       <c r="O7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q7">
-        <v>114</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
@@ -775,16 +775,16 @@
         <v>세종특별자치시</v>
       </c>
       <c r="B8">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C8">
         <v>57</v>
       </c>
       <c r="D8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="F8">
         <v>278</v>
@@ -796,31 +796,31 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>531</v>
+        <v>558</v>
       </c>
       <c r="J8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K8">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="L8">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="M8">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="N8">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="O8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q8">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -831,49 +831,49 @@
         <v>48783</v>
       </c>
       <c r="C9">
-        <v>929</v>
+        <v>946</v>
       </c>
       <c r="D9">
-        <v>1027</v>
+        <v>1064</v>
       </c>
       <c r="E9">
-        <v>3893</v>
+        <v>8777</v>
       </c>
       <c r="F9">
-        <v>1069</v>
+        <v>1128</v>
       </c>
       <c r="G9">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="H9">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>1783</v>
+        <v>1694</v>
       </c>
       <c r="K9">
-        <v>1368</v>
+        <v>1663</v>
       </c>
       <c r="L9">
-        <v>1863</v>
+        <v>1986</v>
       </c>
       <c r="M9">
-        <v>1073</v>
+        <v>1300</v>
       </c>
       <c r="N9">
-        <v>1048</v>
+        <v>1149</v>
       </c>
       <c r="O9">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P9">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="Q9">
-        <v>872</v>
+        <v>991</v>
       </c>
     </row>
     <row r="10">
@@ -881,52 +881,52 @@
         <v>강원특별자치도</v>
       </c>
       <c r="B10">
-        <v>1235</v>
+        <v>1208</v>
       </c>
       <c r="C10">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D10">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E10">
-        <v>232</v>
+        <v>297</v>
       </c>
       <c r="F10">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G10">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I10">
-        <v>2221</v>
+        <v>2109</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="L10">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="M10">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="N10">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="O10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P10">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Q10">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -934,52 +934,52 @@
         <v>충청북도</v>
       </c>
       <c r="B11">
-        <v>1075</v>
+        <v>1253</v>
       </c>
       <c r="C11">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="D11">
-        <v>398</v>
+        <v>345</v>
       </c>
       <c r="E11">
-        <v>214</v>
+        <v>346</v>
       </c>
       <c r="F11">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G11">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H11">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="I11">
-        <v>1696</v>
+        <v>2062</v>
       </c>
       <c r="J11">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="M11">
-        <v>308</v>
+        <v>452</v>
       </c>
       <c r="N11">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="O11">
         <v>21</v>
       </c>
       <c r="P11">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q11">
-        <v>171</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -987,52 +987,52 @@
         <v>충청남도</v>
       </c>
       <c r="B12">
-        <v>1632</v>
+        <v>1668</v>
       </c>
       <c r="C12">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D12">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E12">
-        <v>382</v>
+        <v>569</v>
       </c>
       <c r="F12">
-        <v>674</v>
+        <v>654</v>
       </c>
       <c r="G12">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H12">
+        <v>276</v>
+      </c>
+      <c r="I12">
+        <v>2392</v>
+      </c>
+      <c r="J12">
+        <v>153</v>
+      </c>
+      <c r="K12">
+        <v>379</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>281</v>
       </c>
-      <c r="I12">
-        <v>2244</v>
-      </c>
-      <c r="J12">
-        <v>149</v>
-      </c>
-      <c r="K12">
-        <v>350</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>204</v>
-      </c>
       <c r="N12">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="O12">
         <v>31</v>
       </c>
       <c r="P12">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="Q12">
-        <v>289</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13">
@@ -1040,52 +1040,52 @@
         <v>경상북도</v>
       </c>
       <c r="B13">
-        <v>808</v>
+        <v>971</v>
       </c>
       <c r="C13">
-        <v>485</v>
+        <v>586</v>
       </c>
       <c r="D13">
-        <v>643</v>
+        <v>1569</v>
       </c>
       <c r="E13">
-        <v>189</v>
+        <v>280</v>
       </c>
       <c r="F13">
-        <v>179</v>
+        <v>283</v>
       </c>
       <c r="G13">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="H13">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="I13">
-        <v>1269</v>
+        <v>1538</v>
       </c>
       <c r="J13">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="K13">
-        <v>294</v>
+        <v>431</v>
       </c>
       <c r="L13">
-        <v>201</v>
+        <v>276</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13">
-        <v>429</v>
+        <v>655</v>
       </c>
       <c r="O13">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="P13">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="Q13">
-        <v>187</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14">
@@ -1093,40 +1093,40 @@
         <v>경상남도</v>
       </c>
       <c r="B14">
-        <v>813</v>
+        <v>877</v>
       </c>
       <c r="C14">
-        <v>1874</v>
+        <v>1415</v>
       </c>
       <c r="D14">
-        <v>950</v>
+        <v>1052</v>
       </c>
       <c r="E14">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="F14">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="G14">
-        <v>441</v>
+        <v>375</v>
       </c>
       <c r="H14">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I14">
-        <v>1210</v>
+        <v>1327</v>
       </c>
       <c r="J14">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="K14">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="L14">
-        <v>290</v>
+        <v>319</v>
       </c>
       <c r="M14">
-        <v>419</v>
+        <v>639</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -1135,10 +1135,10 @@
         <v>62</v>
       </c>
       <c r="P14">
-        <v>392</v>
+        <v>490</v>
       </c>
       <c r="Q14">
-        <v>461</v>
+        <v>706</v>
       </c>
     </row>
     <row r="15">
@@ -1155,19 +1155,19 @@
         <v>40</v>
       </c>
       <c r="E15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F15">
         <v>25</v>
       </c>
       <c r="G15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H15">
         <v>6</v>
       </c>
       <c r="I15">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J15">
         <v>16</v>
@@ -1179,7 +1179,7 @@
         <v>35</v>
       </c>
       <c r="M15">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N15">
         <v>73</v>
@@ -1191,7 +1191,7 @@
         <v>40</v>
       </c>
       <c r="Q15">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -1199,43 +1199,43 @@
         <v>전북특별자치도</v>
       </c>
       <c r="B16">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C16">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D16">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="E16">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="F16">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="G16">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H16">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16">
-        <v>994</v>
+        <v>1024</v>
       </c>
       <c r="J16">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K16">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L16">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="M16">
-        <v>169</v>
+        <v>254</v>
       </c>
       <c r="N16">
-        <v>417</v>
+        <v>521</v>
       </c>
       <c r="O16">
         <v>36</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>435</v>
+        <v>642</v>
       </c>
     </row>
     <row r="17">
@@ -1252,49 +1252,49 @@
         <v>전남광주통합특별시</v>
       </c>
       <c r="B17">
-        <v>709</v>
+        <v>785</v>
       </c>
       <c r="C17">
-        <v>343</v>
+        <v>438</v>
       </c>
       <c r="D17">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="E17">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="F17">
-        <v>194</v>
+        <v>245</v>
       </c>
       <c r="G17">
+        <v>127</v>
+      </c>
+      <c r="H17">
+        <v>57</v>
+      </c>
+      <c r="I17">
+        <v>1147</v>
+      </c>
+      <c r="J17">
+        <v>108</v>
+      </c>
+      <c r="K17">
+        <v>190</v>
+      </c>
+      <c r="L17">
+        <v>322</v>
+      </c>
+      <c r="M17">
+        <v>285</v>
+      </c>
+      <c r="N17">
+        <v>707</v>
+      </c>
+      <c r="O17">
         <v>102</v>
       </c>
-      <c r="H17">
-        <v>47</v>
-      </c>
-      <c r="I17">
-        <v>1009</v>
-      </c>
-      <c r="J17">
-        <v>93</v>
-      </c>
-      <c r="K17">
-        <v>160</v>
-      </c>
-      <c r="L17">
-        <v>277</v>
-      </c>
-      <c r="M17">
-        <v>182</v>
-      </c>
-      <c r="N17">
-        <v>461</v>
-      </c>
-      <c r="O17">
-        <v>121</v>
-      </c>
       <c r="P17">
-        <v>410</v>
+        <v>604</v>
       </c>
       <c r="Q17">
         <v>0</v>
